--- a/reports/一级子公司B_利润表_2026-11.xlsx
+++ b/reports/一级子公司B_利润表_2026-11.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>47791004</v>
+        <v>63512805</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>0</v>
+        <v>14247380</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>0</v>
+        <v>162834223</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>0</v>
+        <v>199058</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>0</v>
+        <v>2293963</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>0</v>
+        <v>178871</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>0</v>
+        <v>2063558</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0</v>
+        <v>148966</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>0</v>
+        <v>1718782</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>0</v>
+        <v>139097</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>0</v>
+        <v>1603537</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>0</v>
+        <v>79597</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>0</v>
+        <v>916071</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>0</v>
+        <v>59826</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>0</v>
+        <v>687012</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>47791004</v>
+        <v>62707390</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0</v>
+        <v>13441965</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>0</v>
+        <v>8031205</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>0</v>
+        <v>91688739</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>0</v>
+        <v>1205941</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>0</v>
+        <v>13760224</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>0</v>
+        <v>602983</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>0</v>
+        <v>6883254</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>0</v>
+        <v>4015835</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>0</v>
+        <v>45903564</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>0</v>
+        <v>400836</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>0</v>
+        <v>4591031</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>0</v>
+        <v>299909</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>0</v>
+        <v>3443059</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>0</v>
+        <v>498599</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>0</v>
+        <v>5736931</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>0</v>
+        <v>398013</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>0</v>
+        <v>4587645</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>47708287</v>
+        <v>47692076</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>539115576</v>
+        <v>539105423</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>82717</v>
+        <v>81906</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>906949</v>
+        <v>905826</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>894315</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>10307996</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>597128</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>6870398</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>44041329</v>
+        <v>57136324</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>24978968</v>
+        <v>32318901</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>149892</v>
+        <v>7216530</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1719024</v>
+        <v>82486539</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>24829076</v>
+        <v>25102371</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>286469508</v>
+        <v>286546308</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1507522</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>17201401</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>482349</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>5506896</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>301126</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3442875</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>360646</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>4131944</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>269827</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3098678</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>179439</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2065197</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>149219</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1720258</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1198331</v>
+        <v>1192154</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>13760808</v>
+        <v>13755201</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>40203</v>
+        <v>39725</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>458770</v>
+        <v>458287</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>2493961</v>
+        <v>2484590</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>28646648</v>
+        <v>28632130</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>14904557</v>
+        <v>14932129</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>181741872</v>
+        <v>181671725</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>0</v>
+        <v>2494381</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>0</v>
+        <v>28626172</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>465512</v>
+        <v>464041</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>5099476</v>
+        <v>5093220</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>410017</v>
+        <v>413433</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>4529083</v>
+        <v>4529259</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>30816</v>
+        <v>31060</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>339908</v>
+        <v>339878</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>139880</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1530287</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>263760</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3011736</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>93111</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1020966</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>69691</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>765787</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>115866</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1276114</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>373714</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>4302276</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>61519</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>680009</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>46084</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>509725</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>76791</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>849107</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>53799</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>594147</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>38495</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>424314</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>30869</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>339472</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>23210</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>254673</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>3749675</v>
+        <v>6501828</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>-107378</v>
+        <v>4508931</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>150763</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1720360</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>38841</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>425298</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>61598</v>
+        <v>62060</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>679771</v>
+        <v>680662</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>3688077</v>
+        <v>6590531</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>1856620</v>
+        <v>1853233</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>20390446</v>
+        <v>20417085</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>1831457</v>
+        <v>4737298</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>1831457</v>
+        <v>4737298</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>1831457</v>
+        <v>4737298</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>1831457</v>
+        <v>4737298</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>1831457</v>
+        <v>4737298</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
